--- a/data/trans_dic/IP16_n_R2-Edad-trans_dic.xlsx
+++ b/data/trans_dic/IP16_n_R2-Edad-trans_dic.xlsx
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>15,73; 41,07</t>
+          <t>15,03; 40,14</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>10,75; 33,66</t>
+          <t>10,96; 33,25</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>7,1; 29,19</t>
+          <t>6,77; 29,56</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>34,77; 71,03</t>
+          <t>34,61; 70,52</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>16,61; 44,88</t>
+          <t>15,63; 44,16</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>7,74; 30,65</t>
+          <t>7,32; 29,23</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>12,86; 42,02</t>
+          <t>12,69; 42,37</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>22,21; 51,93</t>
+          <t>22,5; 50,61</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>18,82; 36,79</t>
+          <t>19,52; 38,88</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>11,4; 26,39</t>
+          <t>11,37; 26,22</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>12,14; 29,92</t>
+          <t>12,92; 30,27</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>31,36; 53,02</t>
+          <t>30,2; 54,87</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>29,64; 54,16</t>
+          <t>29,56; 53,41</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>10,03; 28,12</t>
+          <t>9,06; 27,25</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>7,15; 24,58</t>
+          <t>7,37; 25,26</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>18,3; 39,95</t>
+          <t>17,52; 39,59</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>30,02; 51,82</t>
+          <t>30,91; 53,73</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>6,94; 20,55</t>
+          <t>7,32; 20,96</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>4,03; 18,47</t>
+          <t>3,13; 18,43</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>31,1; 54,64</t>
+          <t>31,12; 55,22</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>33,3; 50,14</t>
+          <t>33,32; 50,3</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>9,66; 20,8</t>
+          <t>9,71; 20,62</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>7,35; 18,63</t>
+          <t>7,26; 18,47</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>27,48; 44,53</t>
+          <t>26,98; 44,11</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>23,02; 55,59</t>
+          <t>23,87; 56,51</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>4,08; 23,19</t>
+          <t>3,92; 22,76</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>4,56; 22,59</t>
+          <t>4,72; 23,9</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>35,4; 62,46</t>
+          <t>36,01; 61,81</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>25,7; 58,54</t>
+          <t>26,4; 59,65</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>2,38; 22,68</t>
+          <t>2,31; 22,2</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>4,27; 24,54</t>
+          <t>4,11; 24,92</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>16,17; 40,35</t>
+          <t>13,97; 38,92</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>28,35; 52,05</t>
+          <t>29,0; 53,3</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>4,54; 17,64</t>
+          <t>4,79; 19,09</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>6,37; 19,37</t>
+          <t>6,18; 18,78</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>27,0; 45,53</t>
+          <t>28,38; 46,7</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>32,42; 61,39</t>
+          <t>31,4; 62,02</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>13,51; 40,97</t>
+          <t>12,9; 42,31</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 18,43</t>
+          <t>0,0; 19,0</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>5,08; 27,53</t>
+          <t>4,62; 26,8</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>32,72; 57,19</t>
+          <t>31,62; 57,14</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>7,67; 31,35</t>
+          <t>7,63; 31,49</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>5,57; 32,04</t>
+          <t>5,77; 32,27</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>20,9; 43,35</t>
+          <t>21,61; 44,13</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>35,92; 54,58</t>
+          <t>36,36; 54,22</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>12,71; 32,14</t>
+          <t>12,33; 32,0</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>4,45; 19,87</t>
+          <t>4,28; 19,8</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>11,72; 31,55</t>
+          <t>12,62; 31,59</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>31,2; 45,46</t>
+          <t>31,69; 45,59</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>13,31; 24,09</t>
+          <t>12,8; 23,93</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>8,86; 17,99</t>
+          <t>8,15; 17,78</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>16,74; 36,68</t>
+          <t>17,21; 36,28</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>33,21; 45,73</t>
+          <t>33,45; 46,05</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>9,47; 18,56</t>
+          <t>9,66; 19,02</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>9,48; 19,58</t>
+          <t>9,32; 19,79</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>27,42; 40,25</t>
+          <t>27,46; 39,93</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>34,62; 44,5</t>
+          <t>34,24; 43,93</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>12,07; 19,5</t>
+          <t>12,31; 19,62</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>10,06; 17,16</t>
+          <t>10,05; 16,86</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>24,05; 35,86</t>
+          <t>23,89; 36,22</t>
         </is>
       </c>
     </row>
@@ -1645,62 +1645,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>4566; 11923</t>
+          <t>4365; 11655</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>3925; 12286</t>
+          <t>4001; 12136</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>1918; 7890</t>
+          <t>1831; 7991</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>5558; 11352</t>
+          <t>5532; 11272</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>4927; 13308</t>
+          <t>4635; 13095</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>2974; 11779</t>
+          <t>2813; 11232</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>3084; 10074</t>
+          <t>3043; 10159</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>4965; 11609</t>
+          <t>5031; 11315</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>11045; 21592</t>
+          <t>11459; 22819</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>8538; 19774</t>
+          <t>8519; 19642</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>6191; 15260</t>
+          <t>6592; 15440</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>12022; 20327</t>
+          <t>11578; 21037</t>
         </is>
       </c>
     </row>
@@ -1853,62 +1853,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>12812; 23407</t>
+          <t>12776; 23083</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>5432; 15234</t>
+          <t>4910; 14759</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>3020; 10380</t>
+          <t>3114; 10672</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>8530; 18625</t>
+          <t>8168; 18460</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>15298; 26406</t>
+          <t>15752; 27378</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>4672; 13841</t>
+          <t>4934; 14119</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>1736; 7960</t>
+          <t>1349; 7941</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>15235; 26763</t>
+          <t>15242; 27048</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>31360; 47223</t>
+          <t>31382; 47375</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>11739; 25280</t>
+          <t>11798; 25063</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>6269; 15895</t>
+          <t>6195; 15765</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>26272; 42573</t>
+          <t>25796; 42168</t>
         </is>
       </c>
     </row>
@@ -2061,62 +2061,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>5181; 12511</t>
+          <t>5373; 12720</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>1218; 6926</t>
+          <t>1172; 6798</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>1647; 8159</t>
+          <t>1703; 8634</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>13153; 23204</t>
+          <t>13380; 22965</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>6134; 13970</t>
+          <t>6300; 14237</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>664; 6330</t>
+          <t>644; 6197</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>1429; 8208</t>
+          <t>1376; 8334</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>7466; 18631</t>
+          <t>6451; 17968</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>13148; 24138</t>
+          <t>13446; 24718</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>2625; 10193</t>
+          <t>2767; 11029</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>4434; 13477</t>
+          <t>4301; 13063</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>22500; 37933</t>
+          <t>23645; 38913</t>
         </is>
       </c>
     </row>
@@ -2269,62 +2269,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>9903; 18749</t>
+          <t>9590; 18943</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>3671; 11131</t>
+          <t>3505; 11495</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0; 4067</t>
+          <t>0; 4192</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>3960; 21459</t>
+          <t>3602; 20893</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>12903; 22555</t>
+          <t>12470; 22535</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>1908; 7796</t>
+          <t>1896; 7831</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>1267; 7291</t>
+          <t>1312; 7345</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>13523; 28044</t>
+          <t>13981; 28546</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>25136; 38194</t>
+          <t>25447; 37946</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>6614; 16725</t>
+          <t>6419; 16654</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>1996; 8904</t>
+          <t>1917; 8876</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>16714; 45008</t>
+          <t>17998; 45067</t>
         </is>
       </c>
     </row>
@@ -2477,62 +2477,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>39093; 56965</t>
+          <t>39714; 57125</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>19656; 35575</t>
+          <t>18904; 35340</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>11295; 22928</t>
+          <t>10393; 22664</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>29750; 65193</t>
+          <t>30581; 64467</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>47798; 65808</t>
+          <t>48140; 66271</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>15011; 29427</t>
+          <t>15323; 30154</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>11687; 24135</t>
+          <t>11485; 24391</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>49952; 73332</t>
+          <t>50027; 72760</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>93218; 119813</t>
+          <t>92190; 118258</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>36973; 59728</t>
+          <t>37709; 60077</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>25228; 43032</t>
+          <t>25200; 42264</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>86563; 129050</t>
+          <t>85984; 130359</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/IP16_n_R2-Edad-trans_dic.xlsx
+++ b/data/trans_dic/IP16_n_R2-Edad-trans_dic.xlsx
@@ -527,13 +527,13 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que consumen más de dos medicamentos (tasa de respuesta: 99,76%)</t>
+          <t>Menores que consumieron más de dos medicamentos en las últimas 2 semanas (tasa de respuesta: 99,76%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -541,7 +541,7 @@
       <c r="F1" s="3" t="n"/>
       <c r="G1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="H1" s="3" t="n"/>
@@ -649,42 +649,42 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>28,78%</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>16,65%</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>24,78%</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>35,4%</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
           <t>26,48%</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>19,63%</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="I4" s="2" t="inlineStr">
         <is>
           <t>16,18%</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>51,9%</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>28,78%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>16,65%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>24,78%</t>
-        </is>
-      </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>34,9%</t>
+          <t>53,07%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>41,99%</t>
+          <t>43,32%</t>
         </is>
       </c>
     </row>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>15,03; 40,14</t>
+          <t>16,55; 43,38</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>10,96; 33,25</t>
+          <t>8,03; 28,8</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>6,77; 29,56</t>
+          <t>13,34; 40,72</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>34,61; 70,52</t>
+          <t>20,97; 50,7</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>15,63; 44,16</t>
+          <t>14,26; 39,97</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>7,32; 29,23</t>
+          <t>10,73; 32,15</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>12,69; 42,37</t>
+          <t>7,51; 30,08</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>22,5; 50,61</t>
+          <t>32,01; 71,05</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>19,52; 38,88</t>
+          <t>19,14; 37,16</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>11,37; 26,22</t>
+          <t>11,42; 26,59</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>12,92; 30,27</t>
+          <t>12,72; 30,58</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>30,2; 54,87</t>
+          <t>32,09; 55,8</t>
         </is>
       </c>
     </row>
@@ -789,42 +789,42 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>41,15%</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>12,76%</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>9,21%</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>43,95%</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
           <t>41,02%</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="H6" s="2" t="inlineStr">
         <is>
           <t>17,16%</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="I6" s="2" t="inlineStr">
         <is>
           <t>14,57%</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>27,93%</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>41,15%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>12,76%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>9,21%</t>
-        </is>
-      </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>42,09%</t>
+          <t>29,56%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>35,18%</t>
+          <t>36,78%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>29,56; 53,41</t>
+          <t>29,67; 52,23</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>9,06; 27,25</t>
+          <t>7,26; 20,63</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>7,37; 25,26</t>
+          <t>4,11; 17,73</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>17,52; 39,59</t>
+          <t>32,2; 56,34</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>30,91; 53,73</t>
+          <t>29,98; 52,81</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>7,32; 20,96</t>
+          <t>9,48; 27,19</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>3,13; 18,43</t>
+          <t>6,99; 24,17</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>31,12; 55,22</t>
+          <t>18,46; 40,97</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>33,32; 50,3</t>
+          <t>33,46; 49,09</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>9,71; 20,62</t>
+          <t>9,86; 20,71</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>7,26; 18,47</t>
+          <t>6,8; 18,32</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>26,98; 44,11</t>
+          <t>28,63; 45,22</t>
         </is>
       </c>
     </row>
@@ -929,42 +929,42 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>41,96%</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>8,73%</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>11,17%</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>26,32%</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
           <t>38,86%</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>10,92%</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="I8" s="2" t="inlineStr">
         <is>
           <t>11,53%</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>48,97%</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>41,96%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>8,73%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>11,17%</t>
-        </is>
-      </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>25,66%</t>
+          <t>48,6%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>36,05%</t>
+          <t>36,64%</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>23,87; 56,51</t>
+          <t>26,88; 57,82</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>3,92; 22,76</t>
+          <t>2,37; 21,9</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>4,72; 23,9</t>
+          <t>4,15; 23,85</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>36,01; 61,81</t>
+          <t>14,58; 39,35</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>26,4; 59,65</t>
+          <t>22,68; 55,15</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>2,31; 22,2</t>
+          <t>3,86; 23,34</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>4,11; 24,92</t>
+          <t>4,76; 22,53</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>13,97; 38,92</t>
+          <t>35,57; 64,5</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>29,0; 53,3</t>
+          <t>29,94; 52,88</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>4,79; 19,09</t>
+          <t>4,46; 19,19</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>6,18; 18,78</t>
+          <t>5,97; 20,22</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>28,38; 46,7</t>
+          <t>27,2; 46,46</t>
         </is>
       </c>
     </row>
@@ -1069,42 +1069,42 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>45,0%</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>17,74%</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>14,73%</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>32,23%</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
           <t>45,09%</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>24,85%</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="I10" s="2" t="inlineStr">
         <is>
           <t>5,87%</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>14,31%</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>45,0%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>17,74%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>14,73%</t>
-        </is>
-      </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>32,37%</t>
+          <t>23,17%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>22,5%</t>
+          <t>28,2%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>31,4; 62,02</t>
+          <t>33,19; 57,52</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>12,9; 42,31</t>
+          <t>7,45; 33,24</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 19,0</t>
+          <t>5,63; 31,1</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>4,62; 26,8</t>
+          <t>21,75; 44,48</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>31,62; 57,14</t>
+          <t>32,5; 61,34</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>7,63; 31,49</t>
+          <t>11,48; 40,95</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>5,77; 32,27</t>
+          <t>0,0; 19,48</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>21,61; 44,13</t>
+          <t>13,91; 34,4</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>36,36; 54,22</t>
+          <t>36,24; 55,39</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>12,33; 32,0</t>
+          <t>13,24; 31,31</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>4,28; 19,8</t>
+          <t>4,39; 19,74</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>12,62; 31,59</t>
+          <t>20,96; 37,03</t>
         </is>
       </c>
     </row>
@@ -1209,42 +1209,42 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>39,79%</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>13,78%</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>13,79%</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>33,92%</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
           <t>38,26%</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="H12" s="2" t="inlineStr">
         <is>
           <t>17,92%</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="I12" s="2" t="inlineStr">
         <is>
           <t>12,54%</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>28,51%</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>39,79%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>13,78%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>13,79%</t>
-        </is>
-      </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>33,59%</t>
+          <t>34,71%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>31,08%</t>
+          <t>34,29%</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>31,69; 45,59</t>
+          <t>33,39; 46,14</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>12,8; 23,93</t>
+          <t>9,62; 18,94</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>8,15; 17,78</t>
+          <t>9,34; 19,39</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>17,21; 36,28</t>
+          <t>27,97; 40,39</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>33,45; 46,05</t>
+          <t>31,22; 45,53</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>9,66; 19,02</t>
+          <t>13,13; 23,57</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>9,32; 19,79</t>
+          <t>8,02; 17,78</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>27,46; 39,93</t>
+          <t>28,14; 40,78</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>34,24; 43,93</t>
+          <t>34,4; 44,24</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>12,31; 19,62</t>
+          <t>12,48; 19,8</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>10,05; 16,86</t>
+          <t>9,91; 17,11</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>23,89; 36,22</t>
+          <t>30,27; 39,25</t>
         </is>
       </c>
     </row>
@@ -1387,13 +1387,13 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que consumen más de dos medicamentos (tasa de respuesta: 99,76%)</t>
+          <t>Menores que consumieron más de dos medicamentos en las últimas 2 semanas (tasa de respuesta: 99,76%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -1401,7 +1401,7 @@
       <c r="F1" s="3" t="n"/>
       <c r="G1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="H1" s="3" t="n"/>
@@ -1509,42 +1509,42 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
           <t>13</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>11</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="I4" s="2" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
+      <c r="J4" s="2" t="inlineStr">
         <is>
           <t>16</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>18</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -1577,42 +1577,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>8534</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>6397</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>5941</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>6171</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
           <t>7688</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="H5" s="2" t="inlineStr">
         <is>
           <t>7163</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="I5" s="2" t="inlineStr">
         <is>
           <t>4375</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>8296</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>8534</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>6397</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>5941</t>
-        </is>
-      </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>7803</t>
+          <t>7519</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -1632,7 +1632,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>16099</t>
+          <t>13690</t>
         </is>
       </c>
     </row>
@@ -1645,62 +1645,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>4365; 11655</t>
+          <t>4907; 12865</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>4001; 12136</t>
+          <t>3086; 11067</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>1831; 7991</t>
+          <t>3198; 9763</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>5532; 11272</t>
+          <t>3655; 8838</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>4635; 13095</t>
+          <t>4141; 11606</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>2813; 11232</t>
+          <t>3917; 11733</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>3043; 10159</t>
+          <t>2030; 8131</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>5031; 11315</t>
+          <t>4535; 10067</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>11459; 22819</t>
+          <t>11235; 21808</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>8519; 19642</t>
+          <t>8557; 19922</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>6592; 15440</t>
+          <t>6490; 15599</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>11578; 21037</t>
+          <t>10142; 17633</t>
         </is>
       </c>
     </row>
@@ -1717,42 +1717,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
           <t>26</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="H7" s="2" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="I7" s="2" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
+      <c r="J7" s="2" t="inlineStr">
         <is>
           <t>23</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>31</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>32</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
@@ -1785,42 +1785,42 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>20969</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>8597</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>3968</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>18123</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
           <t>17731</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>9293</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="I8" s="2" t="inlineStr">
         <is>
           <t>6153</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>13022</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>20969</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>8597</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>3968</t>
-        </is>
-      </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>20617</t>
+          <t>12088</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -1840,7 +1840,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>33639</t>
+          <t>30211</t>
         </is>
       </c>
     </row>
@@ -1853,62 +1853,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>12776; 23083</t>
+          <t>15120; 26616</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>4910; 14759</t>
+          <t>4894; 13900</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>3114; 10672</t>
+          <t>1773; 7641</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>8168; 18460</t>
+          <t>13279; 23232</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>15752; 27378</t>
+          <t>12956; 22825</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>4934; 14119</t>
+          <t>5133; 14728</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>1349; 7941</t>
+          <t>2951; 10209</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>15242; 27048</t>
+          <t>7551; 16754</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>31382; 47375</t>
+          <t>31515; 46233</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>11798; 25063</t>
+          <t>11985; 25170</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>6195; 15765</t>
+          <t>5801; 15629</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>25796; 42168</t>
+          <t>23511; 37140</t>
         </is>
       </c>
     </row>
@@ -1925,42 +1925,42 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
           <t>13</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="I10" s="2" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
+      <c r="J10" s="2" t="inlineStr">
         <is>
           <t>27</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>13</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1993,42 +1993,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>10013</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>2438</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>3737</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>11575</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
           <t>8747</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="H11" s="2" t="inlineStr">
         <is>
           <t>3263</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
+      <c r="I11" s="2" t="inlineStr">
         <is>
           <t>4166</t>
         </is>
       </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>18192</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>10013</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>2438</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>3737</t>
-        </is>
-      </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>11846</t>
+          <t>18441</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -2048,7 +2048,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>30038</t>
+          <t>30016</t>
         </is>
       </c>
     </row>
@@ -2061,62 +2061,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>5373; 12720</t>
+          <t>6414; 13800</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>1172; 6798</t>
+          <t>661; 6114</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>1703; 8634</t>
+          <t>1387; 7978</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>13380; 22965</t>
+          <t>6410; 17302</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>6300; 14237</t>
+          <t>5106; 12412</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>644; 6197</t>
+          <t>1153; 6970</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>1376; 8334</t>
+          <t>1720; 8140</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>6451; 17968</t>
+          <t>13497; 24478</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>13446; 24718</t>
+          <t>13884; 24521</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>2767; 11029</t>
+          <t>2578; 11090</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>4301; 13063</t>
+          <t>4150; 14067</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>23645; 38913</t>
+          <t>22280; 38059</t>
         </is>
       </c>
     </row>
@@ -2133,42 +2133,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
           <t>20</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="H13" s="2" t="inlineStr">
         <is>
           <t>9</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="I13" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="F13" s="2" t="inlineStr">
+      <c r="J13" s="2" t="inlineStr">
         <is>
           <t>16</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>26</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>27</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
@@ -2201,42 +2201,42 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>17747</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>4412</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>3352</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>20086</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
           <t>13771</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="H14" s="2" t="inlineStr">
         <is>
           <t>6751</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="I14" s="2" t="inlineStr">
         <is>
           <t>1296</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>11153</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>17747</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>4412</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>3352</t>
-        </is>
-      </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>20939</t>
+          <t>11580</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2256,7 +2256,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>32092</t>
+          <t>31666</t>
         </is>
       </c>
     </row>
@@ -2269,62 +2269,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>9590; 18943</t>
+          <t>13091; 22686</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>3505; 11495</t>
+          <t>1853; 8265</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0; 4192</t>
+          <t>1281; 7077</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>3602; 20893</t>
+          <t>13555; 27719</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>12470; 22535</t>
+          <t>9926; 18736</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>1896; 7831</t>
+          <t>3120; 11126</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>1312; 7345</t>
+          <t>0; 4297</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>13981; 28546</t>
+          <t>6950; 17191</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>25447; 37946</t>
+          <t>25359; 38763</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>6419; 16654</t>
+          <t>6889; 16291</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>1917; 8876</t>
+          <t>1966; 8849</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>17998; 45067</t>
+          <t>23533; 41579</t>
         </is>
       </c>
     </row>
@@ -2341,42 +2341,42 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>84</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>90</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
           <t>72</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="H16" s="2" t="inlineStr">
         <is>
           <t>37</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
+      <c r="I16" s="2" t="inlineStr">
         <is>
           <t>25</t>
         </is>
       </c>
-      <c r="F16" s="2" t="inlineStr">
+      <c r="J16" s="2" t="inlineStr">
         <is>
           <t>82</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>84</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>26</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>90</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -2409,42 +2409,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>57263</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>21844</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>16998</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>55955</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
           <t>47937</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="H17" s="2" t="inlineStr">
         <is>
           <t>26470</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
+      <c r="I17" s="2" t="inlineStr">
         <is>
           <t>15989</t>
         </is>
       </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>50663</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>57263</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>21844</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>16998</t>
-        </is>
-      </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>61204</t>
+          <t>49628</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -2464,7 +2464,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>111868</t>
+          <t>105583</t>
         </is>
       </c>
     </row>
@@ -2477,62 +2477,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>39714; 57125</t>
+          <t>48060; 66398</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>18904; 35340</t>
+          <t>15257; 30041</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>10393; 22664</t>
+          <t>11520; 23909</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>30581; 64467</t>
+          <t>46133; 66628</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>48140; 66271</t>
+          <t>39115; 57055</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>15323; 30154</t>
+          <t>19392; 34820</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>11485; 24391</t>
+          <t>10223; 22667</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>50027; 72760</t>
+          <t>40244; 58311</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>92190; 118258</t>
+          <t>92603; 119116</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>37709; 60077</t>
+          <t>38212; 60635</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>25200; 42264</t>
+          <t>24849; 42911</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>85984; 130359</t>
+          <t>93209; 120878</t>
         </is>
       </c>
     </row>
